--- a/Diadoc_status.xlsx
+++ b/Diadoc_status.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$V$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$V$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -645,30 +645,30 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>"9705124940"</f>
+        <f>"7730245060"</f>
         <v/>
       </c>
       <c r="B3">
-        <f>"773601001"</f>
+        <f>"773001001"</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ООО "СБЕР ЛИГАЛ"</t>
+          <t>ООО "МЕДЭКСПЕРТ ПЛЮС"</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9705124940 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7730245060 от 20.04.26</t>
         </is>
       </c>
       <c r="E3">
-        <f>"LBO-LE-9705124940"</f>
+        <f>"LBS-LE-7730245060"</f>
         <v/>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>20.04.2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -683,7 +683,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>21.04.2026 18:03:03</t>
+          <t>20.04.2026 18:04:09</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -694,7 +694,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>21.04.2026 18:03:03</t>
+          <t>20.04.2026 18:04:09</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -710,37 +710,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=d9678593-5fe8-45ce-9ebb-671ce2ae2b67&amp;documentId=7c63b886-3d88-4244-b460-955191f0fa6a</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=3384ddbb-db75-49b3-9a2e-1498b1d49a11&amp;documentId=28be2f88-913f-4af5-b911-ac546d0ae3fd</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2BM-9705124940-770501001-201902010233255673854</t>
+          <t>2BM-7730245060-773001001-201807250544240340948</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <f>"7730335860"</f>
+        <f>"9705124940"</f>
         <v/>
       </c>
       <c r="B4">
-        <f>"770601001"</f>
+        <f>"773601001"</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>АО "ЦИФРОВОЙ СЕМЕЙНЫЙ ОФИС"</t>
+          <t>ООО "СБЕР ЛИГАЛ"</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7730335860 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-9705124940 от 21.04.26</t>
         </is>
       </c>
       <c r="E4">
-        <f>"LBO-LE-7730335860"</f>
+        <f>"LBO-LE-9705124940"</f>
         <v/>
       </c>
       <c r="F4" t="inlineStr">
@@ -787,37 +787,37 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=67f04bcf-6bba-4542-af6b-78070329fef7&amp;documentId=10745677-ce18-4c19-812f-31aaff61026a</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=d9678593-5fe8-45ce-9ebb-671ce2ae2b67&amp;documentId=7c63b886-3d88-4244-b460-955191f0fa6a</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2BM-7730335860-773001001-202503200138347929328</t>
+          <t>2BM-9705124940-770501001-201902010233255673854</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <f>"7714843760"</f>
+        <f>"7730335860"</f>
         <v/>
       </c>
       <c r="B5">
-        <f>"771001001"</f>
+        <f>"770601001"</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ООО "Инсейлс Рус"</t>
+          <t>АО "ЦИФРОВОЙ СЕМЕЙНЫЙ ОФИС"</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7714843760 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7730335860 от 21.04.26</t>
         </is>
       </c>
       <c r="E5">
-        <f>"LBO-LE-7714843760"</f>
+        <f>"LBO-LE-7730335860"</f>
         <v/>
       </c>
       <c r="F5" t="inlineStr">
@@ -864,37 +864,37 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=c545483d-b84c-4379-9654-e90362ab9dd3&amp;documentId=51e09292-11ff-4bbf-a70e-1a5f692893c7</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=67f04bcf-6bba-4542-af6b-78070329fef7&amp;documentId=10745677-ce18-4c19-812f-31aaff61026a</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2BM-7714843760-771401001-201407070405496642694</t>
+          <t>2BM-7730335860-773001001-202503200138347929328</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <f>"7743001840"</f>
+        <f>"7714843760"</f>
         <v/>
       </c>
       <c r="B6">
-        <f>"997750001"</f>
+        <f>"771001001"</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ООО "ВК"</t>
+          <t>ООО "Инсейлс Рус"</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7743001840 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7714843760 от 21.04.26</t>
         </is>
       </c>
       <c r="E6">
-        <f>"LBO-LE-7743001840"</f>
+        <f>"LBO-LE-7714843760"</f>
         <v/>
       </c>
       <c r="F6" t="inlineStr">
@@ -941,37 +941,37 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=464a0ef3-a676-4b2a-aafc-f4b9f5dda61c&amp;documentId=f36e3345-bdef-4c80-8dad-5b647cf49358</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=c545483d-b84c-4379-9654-e90362ab9dd3&amp;documentId=51e09292-11ff-4bbf-a70e-1a5f692893c7</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2BM-7743001840-2012052807514600749280000000000</t>
+          <t>2BM-7714843760-771401001-201407070405496642694</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <f>"9731053950"</f>
+        <f>"7743001840"</f>
         <v/>
       </c>
       <c r="B7">
-        <f>"772501001"</f>
+        <f>"997750001"</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ООО "СБЕР РЕШЕНИЯ"</t>
+          <t>ООО "ВК"</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9731053950 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7743001840 от 21.04.26</t>
         </is>
       </c>
       <c r="E7">
-        <f>"LBO-LE-9731053950"</f>
+        <f>"LBO-LE-7743001840"</f>
         <v/>
       </c>
       <c r="F7" t="inlineStr">
@@ -1018,37 +1018,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=d96ef8b1-de67-4271-9600-2c084e39998f&amp;documentId=f4267f25-05be-424a-ba9a-b54aa3a14b17</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=464a0ef3-a676-4b2a-aafc-f4b9f5dda61c&amp;documentId=f36e3345-bdef-4c80-8dad-5b647cf49358</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2BM-9731053950-773101001-202004010137003804688</t>
+          <t>2BM-7743001840-2012052807514600749280000000000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <f>"7714700709"</f>
+        <f>"9731053950"</f>
         <v/>
       </c>
       <c r="B8">
-        <f>"771401001"</f>
+        <f>"772501001"</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ООО "БОРИСХОФ ХОЛДИНГ"</t>
+          <t>ООО "СБЕР РЕШЕНИЯ"</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7714700709 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-9731053950 от 21.04.26</t>
         </is>
       </c>
       <c r="E8">
-        <f>"LBO-LE-7714700709"</f>
+        <f>"LBO-LE-9731053950"</f>
         <v/>
       </c>
       <c r="F8" t="inlineStr">
@@ -1095,37 +1095,37 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=c580ed5c-578b-49c9-aec6-b889991efed0&amp;documentId=c4dd8965-f073-4088-80ff-e7f1c44d440b</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=d96ef8b1-de67-4271-9600-2c084e39998f&amp;documentId=f4267f25-05be-424a-ba9a-b54aa3a14b17</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2BM-7714700709-771401001-201412030938541730816</t>
+          <t>2BM-9731053950-773101001-202004010137003804688</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <f>"7707009586"</f>
+        <f>"7714700709"</f>
         <v/>
       </c>
       <c r="B9">
-        <f>"503201001"</f>
+        <f>"771401001"</f>
         <v/>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>АО "Сбербанк Лизинг"</t>
+          <t>ООО "БОРИСХОФ ХОЛДИНГ"</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7707009586 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7714700709 от 21.04.26</t>
         </is>
       </c>
       <c r="E9">
-        <f>"LBO-LE-7707009586"</f>
+        <f>"LBO-LE-7714700709"</f>
         <v/>
       </c>
       <c r="F9" t="inlineStr">
@@ -1172,37 +1172,37 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=09584062-9f8f-4f2f-928f-8b31b20ef403&amp;documentId=db39c0b2-0943-44cb-9080-f4477d9055c0</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=c580ed5c-578b-49c9-aec6-b889991efed0&amp;documentId=c4dd8965-f073-4088-80ff-e7f1c44d440b</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2BM-7707009586-2013012408391209283140000000000</t>
+          <t>2BM-7714700709-771401001-201412030938541730816</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <f>"6165125468"</f>
+        <f>"7707009586"</f>
         <v/>
       </c>
       <c r="B10">
-        <f>"616101001"</f>
+        <f>"503201001"</f>
         <v/>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ООО "Проф ИТ"</t>
+          <t>АО "Сбербанк Лизинг"</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-6165125468 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7707009586 от 21.04.26</t>
         </is>
       </c>
       <c r="E10">
-        <f>"LBO-LE-6165125468"</f>
+        <f>"LBO-LE-7707009586"</f>
         <v/>
       </c>
       <c r="F10" t="inlineStr">
@@ -1249,37 +1249,37 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=779d1b88-a67b-4cac-a33d-ea1030334d0d&amp;documentId=21dff247-a03e-468f-a3e4-e76e10574333</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=09584062-9f8f-4f2f-928f-8b31b20ef403&amp;documentId=db39c0b2-0943-44cb-9080-f4477d9055c0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2BM-6165125468-2013022203464769820750000000000</t>
+          <t>2BM-7707009586-2013012408391209283140000000000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <f>"7704386240"</f>
+        <f>"6165125468"</f>
         <v/>
       </c>
       <c r="B11">
-        <f>"772601001"</f>
+        <f>"616101001"</f>
         <v/>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ООО "АЛГОРИТМИКА"</t>
+          <t>ООО "Проф ИТ"</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7704386240 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-6165125468 от 21.04.26</t>
         </is>
       </c>
       <c r="E11">
-        <f>"LBO-LE-7704386240"</f>
+        <f>"LBO-LE-6165125468"</f>
         <v/>
       </c>
       <c r="F11" t="inlineStr">
@@ -1326,37 +1326,37 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=b20505c0-38fc-40ec-8430-9b96d1188c2f&amp;documentId=15d9d41c-f0fe-4f0c-9dee-5500a277953d</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=779d1b88-a67b-4cac-a33d-ea1030334d0d&amp;documentId=21dff247-a03e-468f-a3e4-e76e10574333</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2BM-7704386240-770401001-201703311232197576430</t>
+          <t>2BM-6165125468-2013022203464769820750000000000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <f>"7714037217"</f>
+        <f>"7704386240"</f>
         <v/>
       </c>
       <c r="B12">
-        <f>"771501001"</f>
+        <f>"772601001"</f>
         <v/>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>АО "ИД "КОМСОМОЛЬСКАЯ ПРАВДА"</t>
+          <t>ООО "АЛГОРИТМИКА"</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7714037217 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7704386240 от 21.04.26</t>
         </is>
       </c>
       <c r="E12">
-        <f>"LBO-LE-7714037217"</f>
+        <f>"LBO-LE-7704386240"</f>
         <v/>
       </c>
       <c r="F12" t="inlineStr">
@@ -1403,37 +1403,37 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=09428b5b-3d3b-4295-af44-0ff7c7da4a7f&amp;documentId=018b4320-2f22-40f3-9a08-8999ce68a417</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=b20505c0-38fc-40ec-8430-9b96d1188c2f&amp;documentId=15d9d41c-f0fe-4f0c-9dee-5500a277953d</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2BM-7714037217-2013041906494444838870000000000</t>
+          <t>2BM-7704386240-770401001-201703311232197576430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <f>"5405276278"</f>
+        <f>"7714037217"</f>
         <v/>
       </c>
       <c r="B13">
-        <f>"997750001"</f>
+        <f>"771501001"</f>
         <v/>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ООО "ДубльГИС"</t>
+          <t>АО "ИД "КОМСОМОЛЬСКАЯ ПРАВДА"</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-5405276278 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7714037217 от 21.04.26</t>
         </is>
       </c>
       <c r="E13">
-        <f>"LBO-LE-5405276278"</f>
+        <f>"LBO-LE-7714037217"</f>
         <v/>
       </c>
       <c r="F13" t="inlineStr">
@@ -1480,19 +1480,19 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=7ce88d28-d93a-4eb3-b75e-163bcd207b74&amp;documentId=8d4cd5c9-0592-4e0c-a05c-18cfac223467</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=09428b5b-3d3b-4295-af44-0ff7c7da4a7f&amp;documentId=018b4320-2f22-40f3-9a08-8999ce68a417</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2BM-5405276278-2012052807475378365240000000000</t>
+          <t>2BM-7714037217-2013041906494444838870000000000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <f>"7736264044"</f>
+        <f>"5405276278"</f>
         <v/>
       </c>
       <c r="B14">
@@ -1501,16 +1501,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ООО "СБЕРБАНК-ТЕЛЕКОМ"</t>
+          <t>ООО "ДубльГИС"</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7736264044 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-5405276278 от 21.04.26</t>
         </is>
       </c>
       <c r="E14">
-        <f>"LBO-LE-7736264044"</f>
+        <f>"LBO-LE-5405276278"</f>
         <v/>
       </c>
       <c r="F14" t="inlineStr">
@@ -1557,37 +1557,37 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0fb1ab38-75a6-416a-bcd8-254a26b33107&amp;documentId=b31279d3-3c8b-4f37-aedd-a6595e5acd09</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=7ce88d28-d93a-4eb3-b75e-163bcd207b74&amp;documentId=8d4cd5c9-0592-4e0c-a05c-18cfac223467</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2BM-7736264044-773601001-201604250949499477147</t>
+          <t>2BM-5405276278-2012052807475378365240000000000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <f>"7736303529"</f>
+        <f>"7736264044"</f>
         <v/>
       </c>
       <c r="B15">
-        <f>"773001001"</f>
+        <f>"997750001"</f>
         <v/>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ООО "АБТ"</t>
+          <t>ООО "СБЕРБАНК-ТЕЛЕКОМ"</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7736303529 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7736264044 от 21.04.26</t>
         </is>
       </c>
       <c r="E15">
-        <f>"LBO-LE-7736303529"</f>
+        <f>"LBO-LE-7736264044"</f>
         <v/>
       </c>
       <c r="F15" t="inlineStr">
@@ -1634,37 +1634,37 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=f45e8d99-4bd7-4c46-9b9a-ff00ad41dc2f&amp;documentId=9c94b789-c559-43fd-9cb6-98f1544f371e</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0fb1ab38-75a6-416a-bcd8-254a26b33107&amp;documentId=b31279d3-3c8b-4f37-aedd-a6595e5acd09</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2BM-7736303529-773601001-201901151045071718995</t>
+          <t>2BM-7736264044-773601001-201604250949499477147</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <f>"6674330951"</f>
+        <f>"7736303529"</f>
         <v/>
       </c>
       <c r="B16">
-        <f>"667901001"</f>
+        <f>"773001001"</f>
         <v/>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>АО "ГРУППА "СВЭЛ"</t>
+          <t>ООО "АБТ"</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-6674330951 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7736303529 от 21.04.26</t>
         </is>
       </c>
       <c r="E16">
-        <f>"LBO-LE-6674330951"</f>
+        <f>"LBO-LE-7736303529"</f>
         <v/>
       </c>
       <c r="F16" t="inlineStr">
@@ -1711,37 +1711,37 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=49fe7568-ffc3-46a6-aff1-aacb49491fca&amp;documentId=71e7b925-f17b-4bd5-abac-85932f989ad0</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=f45e8d99-4bd7-4c46-9b9a-ff00ad41dc2f&amp;documentId=9c94b789-c559-43fd-9cb6-98f1544f371e</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2BM-6674330951-2012110807072921393260000000000</t>
+          <t>2BM-7736303529-773601001-201901151045071718995</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <f>"7730262964"</f>
+        <f>"6674330951"</f>
         <v/>
       </c>
       <c r="B17">
-        <f>"773001001"</f>
+        <f>"667901001"</f>
         <v/>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ООО "СБЕРОБРАЗОВАНИЕ"</t>
+          <t>АО "ГРУППА "СВЭЛ"</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7730262964 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-6674330951 от 21.04.26</t>
         </is>
       </c>
       <c r="E17">
-        <f>"LBO-LE-7730262964"</f>
+        <f>"LBO-LE-6674330951"</f>
         <v/>
       </c>
       <c r="F17" t="inlineStr">
@@ -1788,37 +1788,37 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=b396ac29-bc8f-4b7a-b50f-57ced74f89f2&amp;documentId=c8866bc5-935b-440c-b30d-7280a0f5b39d</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=49fe7568-ffc3-46a6-aff1-aacb49491fca&amp;documentId=71e7b925-f17b-4bd5-abac-85932f989ad0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2BM-7730262964-773001001-202104080140096713376</t>
+          <t>2BM-6674330951-2012110807072921393260000000000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <f>"7705664765"</f>
+        <f>"7730262964"</f>
         <v/>
       </c>
       <c r="B18">
-        <f>"770701001"</f>
+        <f>"773001001"</f>
         <v/>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ЗАО "Группа компаний С 7"</t>
+          <t>ООО "СБЕРОБРАЗОВАНИЕ"</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7705664765 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7730262964 от 21.04.26</t>
         </is>
       </c>
       <c r="E18">
-        <f>"LBO-LE-7705664765"</f>
+        <f>"LBO-LE-7730262964"</f>
         <v/>
       </c>
       <c r="F18" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=14691c6e-60d1-4bde-9ca0-d9b820425167&amp;documentId=15cd7951-1be1-46f6-90bf-68fa835f6eb2</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=b396ac29-bc8f-4b7a-b50f-57ced74f89f2&amp;documentId=c8866bc5-935b-440c-b30d-7280a0f5b39d</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2BM-7705664765-2012052808342199222630000000000</t>
+          <t>2BM-7730262964-773001001-202104080140096713376</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <f>"9710011437"</f>
+        <f>"7705664765"</f>
         <v/>
       </c>
       <c r="B19">
-        <f>"771001001"</f>
+        <f>"770701001"</f>
         <v/>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ООО "ДОКДОК"</t>
+          <t>ЗАО "Группа компаний С 7"</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9710011437 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7705664765 от 21.04.26</t>
         </is>
       </c>
       <c r="E19">
-        <f>"LBO-LE-9710011437"</f>
+        <f>"LBO-LE-7705664765"</f>
         <v/>
       </c>
       <c r="F19" t="inlineStr">
@@ -1942,37 +1942,37 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=a9e14732-816e-4501-8928-e64a21a4b110&amp;documentId=645b6b5c-47db-40e2-b3f5-f645a1949873</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=14691c6e-60d1-4bde-9ca0-d9b820425167&amp;documentId=15cd7951-1be1-46f6-90bf-68fa835f6eb2</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2BM-9710011437-771001001-201703091137445169969</t>
+          <t>2BM-7705664765-2012052808342199222630000000000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <f>"9706000111"</f>
+        <f>"9710011437"</f>
         <v/>
       </c>
       <c r="B20">
-        <f>"772501001"</f>
+        <f>"771001001"</f>
         <v/>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ООО "ИННОВАЦИОННАЯ МЕДИЦИНА"</t>
+          <t>ООО "ДОКДОК"</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9706000111 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-9710011437 от 21.04.26</t>
         </is>
       </c>
       <c r="E20">
-        <f>"LBO-LE-9706000111"</f>
+        <f>"LBO-LE-9710011437"</f>
         <v/>
       </c>
       <c r="F20" t="inlineStr">
@@ -2019,37 +2019,37 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=279275f3-2bdf-454e-bd89-ae37e09c296f&amp;documentId=16aad7ef-1280-422b-bd8e-07a5764efdb7</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=a9e14732-816e-4501-8928-e64a21a4b110&amp;documentId=645b6b5c-47db-40e2-b3f5-f645a1949873</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2BM-9706000111-770601001-201909050127287045284</t>
+          <t>2BM-9710011437-771001001-201703091137445169969</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <f>"7710183778"</f>
+        <f>"9706000111"</f>
         <v/>
       </c>
       <c r="B21">
-        <f>"770301001"</f>
+        <f>"772501001"</f>
         <v/>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>АО УК "ПЕРВАЯ"</t>
+          <t>ООО "ИННОВАЦИОННАЯ МЕДИЦИНА"</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7710183778 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-9706000111 от 21.04.26</t>
         </is>
       </c>
       <c r="E21">
-        <f>"LBO-LE-7710183778"</f>
+        <f>"LBO-LE-9706000111"</f>
         <v/>
       </c>
       <c r="F21" t="inlineStr">
@@ -2096,37 +2096,37 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=1a474a11-cb39-4ea8-bd52-76c32e4cd1e8&amp;documentId=04fab41d-b7e4-4a61-8245-90609cb6c583</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=279275f3-2bdf-454e-bd89-ae37e09c296f&amp;documentId=16aad7ef-1280-422b-bd8e-07a5764efdb7</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2BM-7710183778-775001001-201409220723375413314</t>
+          <t>2BM-9706000111-770601001-201909050127287045284</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <f>"5024093941"</f>
+        <f>"7710183778"</f>
         <v/>
       </c>
       <c r="B22">
-        <f>"773001001"</f>
+        <f>"770301001"</f>
         <v/>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>АО "СБЕРСИТИ"</t>
+          <t>АО УК "ПЕРВАЯ"</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-5024093941 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7710183778 от 21.04.26</t>
         </is>
       </c>
       <c r="E22">
-        <f>"LBO-LE-5024093941"</f>
+        <f>"LBO-LE-7710183778"</f>
         <v/>
       </c>
       <c r="F22" t="inlineStr">
@@ -2173,37 +2173,37 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=6d47a8ec-f5fa-4587-bbd5-60ce21b27c9a&amp;documentId=56483607-e3a0-42c5-ad6c-bf5bbfec27e7</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=1a474a11-cb39-4ea8-bd52-76c32e4cd1e8&amp;documentId=04fab41d-b7e4-4a61-8245-90609cb6c583</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2BM-5024093941-2012052808331238502630000000000</t>
+          <t>2BM-7710183778-775001001-201409220723375413314</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <f>"7701103751"</f>
+        <f>"5024093941"</f>
         <v/>
       </c>
       <c r="B23">
-        <f>"770101001"</f>
+        <f>"773001001"</f>
         <v/>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>АО "АИФ"</t>
+          <t>АО "СБЕРСИТИ"</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7701103751 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-5024093941 от 21.04.26</t>
         </is>
       </c>
       <c r="E23">
-        <f>"LBO-LE-7701103751"</f>
+        <f>"LBO-LE-5024093941"</f>
         <v/>
       </c>
       <c r="F23" t="inlineStr">
@@ -2250,37 +2250,37 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=933f7ca8-7dbc-4eb9-b628-4aae4852647c&amp;documentId=c5a6c687-437a-4fa3-93c2-957c66982a6d</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=6d47a8ec-f5fa-4587-bbd5-60ce21b27c9a&amp;documentId=56483607-e3a0-42c5-ad6c-bf5bbfec27e7</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2BM-7701103751-2013011012115933921680000000000</t>
+          <t>2BM-5024093941-2012052808331238502630000000000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <f>"9710135746"</f>
+        <f>"7701103751"</f>
         <v/>
       </c>
       <c r="B24">
-        <f>"771001001"</f>
+        <f>"770101001"</f>
         <v/>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ООО "ЭЙАЙЭКСПЕРТ"</t>
+          <t>АО "АИФ"</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9710135746 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7701103751 от 21.04.26</t>
         </is>
       </c>
       <c r="E24">
-        <f>"LBO-LE-9710135746"</f>
+        <f>"LBO-LE-7701103751"</f>
         <v/>
       </c>
       <c r="F24" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>21.04.2026 18:03:11</t>
+          <t>21.04.2026 18:03:03</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2311,7 +2311,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>21.04.2026 18:03:11</t>
+          <t>21.04.2026 18:03:03</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2327,37 +2327,37 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=de40fd4e-8c62-45af-bd94-40f95c3126af&amp;documentId=002b0c6b-7db6-4e31-ab94-43bedb314f52</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=933f7ca8-7dbc-4eb9-b628-4aae4852647c&amp;documentId=c5a6c687-437a-4fa3-93c2-957c66982a6d</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2BM-9710135746-771001001-202408210656584132210</t>
+          <t>2BM-7701103751-2013011012115933921680000000000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <f>"6905062011"</f>
+        <f>"9710135746"</f>
         <v/>
       </c>
       <c r="B25">
-        <f>"997150001"</f>
+        <f>"771001001"</f>
         <v/>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>АО "ДКС"</t>
+          <t>ООО "ЭЙАЙЭКСПЕРТ"</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-6905062011 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-9710135746 от 21.04.26</t>
         </is>
       </c>
       <c r="E25">
-        <f>"LBO-LE-6905062011"</f>
+        <f>"LBO-LE-9710135746"</f>
         <v/>
       </c>
       <c r="F25" t="inlineStr">
@@ -2377,7 +2377,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:14</t>
+          <t>21.04.2026 18:03:11</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2388,7 +2388,7 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:14</t>
+          <t>21.04.2026 18:03:11</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2404,37 +2404,37 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=1db40d2f-58f6-4c1e-a1d8-db3112bdea1d&amp;documentId=d37df6e8-eb17-45ac-b66d-e0b8140e7c9a</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=de40fd4e-8c62-45af-bd94-40f95c3126af&amp;documentId=002b0c6b-7db6-4e31-ab94-43bedb314f52</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2BM-6905062011-2012073010503125473850000000000</t>
+          <t>2BM-9710135746-771001001-202408210656584132210</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <f>"9729292654"</f>
+        <f>"7702454880"</f>
         <v/>
       </c>
       <c r="B26">
-        <f>"772901001"</f>
+        <f>"770901001"</f>
         <v/>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ООО "АДАПТИВНЫЕ ТЕХНОЛОГИИ РАЗВИТИЯ"</t>
+          <t>АО ГК "НЕОЛАНТ"</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9729292654 от 22.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7702454880 от 22.04.26</t>
         </is>
       </c>
       <c r="E26">
-        <f>"LBO-LE-9729292654"</f>
+        <f>"LBS-LE-7702454880"</f>
         <v/>
       </c>
       <c r="F26" t="inlineStr">
@@ -2454,7 +2454,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:14</t>
+          <t>22.04.2026 15:06:53</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2465,7 +2465,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:14</t>
+          <t>22.04.2026 15:06:53</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=2c8edd22-c03c-4fb8-9584-ae2359e06387&amp;documentId=8dad496f-445c-452f-a592-4f4dc8abed59</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=f54147d5-c6b7-49ad-9587-163e11ada05e&amp;documentId=872619d5-dbc4-480c-bbdd-c15dcb0d654d</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2BM-9729292654-772901001-202002050849418300734</t>
+          <t>2BM-7702454880-770201001-201903031009243765727</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <f>"7811753424"</f>
+        <f>"6102061451"</f>
         <v/>
       </c>
       <c r="B27">
-        <f>"781001001"</f>
+        <f>"610201001"</f>
         <v/>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ООО "ОЗБЭТТЕРИЗ"</t>
+          <t>ООО "МИЛЕНД"</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7811753424 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-6102061451 от 22.04.26</t>
         </is>
       </c>
       <c r="E27">
-        <f>"LBO-LE-7811753424"</f>
+        <f>"LBS-LE-6102061451"</f>
         <v/>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:14</t>
+          <t>22.04.2026 15:06:53</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2542,7 +2542,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:14</t>
+          <t>22.04.2026 15:06:53</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2558,42 +2558,42 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=144c8b91-e507-4a0b-b827-17068f1ee5fc&amp;documentId=bbbbc8f5-5a4c-40b5-adad-87aaf989d2c9</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=f66fcafb-74cf-4d55-820b-44dd272c9fc5&amp;documentId=1b5c4622-365a-477e-9a74-f5762cfde553</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2BM-7811753424-781101001-202101280852447862235</t>
+          <t>2BM-6102061451-610201001-201604100423101364178</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <f>"7717586110"</f>
+        <f>"1435236532"</f>
         <v/>
       </c>
       <c r="B28">
-        <f>"770501001"</f>
+        <f>"143501001"</f>
         <v/>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ООО "1С-Битрикс"</t>
+          <t>ГБУ РС (Я) "РЦИТ"</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7717586110 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-1435236532 от 22.04.26</t>
         </is>
       </c>
       <c r="E28">
-        <f>"LBO-LE-7717586110"</f>
+        <f>"LBS-LE-1435236532"</f>
         <v/>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -2608,7 +2608,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:14</t>
+          <t>22.04.2026 15:06:53</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2619,7 +2619,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:14</t>
+          <t>22.04.2026 15:06:53</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2635,37 +2635,37 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=fb29d128-a8f3-49e0-b45d-6cc0247e2f33&amp;documentId=6db8b825-5d93-4467-8506-107415352063</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=7c9f94c4-83db-4d24-9e47-efc9e18b9b2d&amp;documentId=8bf4f919-85ef-4081-84bb-a2adebb1f5bf</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2BM-7717586110-2012052807532742374290000000000</t>
+          <t>2BM-1435236532-143501001-201412080151518070402</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <f>"9731065465"</f>
+        <f>"7713076301"</f>
         <v/>
       </c>
       <c r="B29">
-        <f>"773101001"</f>
+        <f>"997750001"</f>
         <v/>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ООО "СБЕРМЕДИИ"</t>
+          <t>ПАО "ВымпелКом"</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9731065465 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7713076301 от 21.04.26</t>
         </is>
       </c>
       <c r="E29">
-        <f>"LBO-LE-9731065465"</f>
+        <f>"LBS-LE-7713076301"</f>
         <v/>
       </c>
       <c r="F29" t="inlineStr">
@@ -2712,37 +2712,37 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=bf6924e7-71da-4323-8f6d-81bca3bcb9c3&amp;documentId=c4b1a76c-de5c-4fc1-87b9-69cc4738bafe</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=afd91d10-d12a-476e-92f6-6303286ada7b&amp;documentId=c663de3b-435d-4db0-bff3-c7a203deb2d0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2BM-9731065465-773101001-202008251257056035458</t>
+          <t>2BM-7713076301-2012052807251168061080000000000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <f>"3460062918"</f>
+        <f>"1435115880"</f>
         <v/>
       </c>
       <c r="B30">
-        <f>"344401001"</f>
+        <f>"143501001"</f>
         <v/>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ООО "ХЕППИВЕАР ЮГ"</t>
+          <t>АГУИККИ, ФГБОУ ВО "АГУИККИ", АРКТИЧЕСКИЙ ГОСУДАРСТВЕННЫЙ УНИВЕРСИТЕТ ИСКУССТВ, КУЛЬТУРЫ И КРЕАТИВНЫХ ИНДУСТРИЙ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-3460062918 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-1435115880 от 21.04.26</t>
         </is>
       </c>
       <c r="E30">
-        <f>"LBO-LE-3460062918"</f>
+        <f>"LBS-LE-1435115880"</f>
         <v/>
       </c>
       <c r="F30" t="inlineStr">
@@ -2789,19 +2789,19 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=476672fa-2286-4a4e-bc9e-ef89d5c281e8&amp;documentId=1c073372-724b-475e-a4b2-0fe51ee8c49b</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=89da7ad4-2353-4e10-822b-236c5be3296d&amp;documentId=a0ec4ecb-578d-42a3-98b2-2d372ceec49c</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2BM-3460062918-346001001-201701161254302210381</t>
+          <t>2BM-1435115880-2012052808301594902630000000000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <f>"5045016560"</f>
+        <f>"6905062011"</f>
         <v/>
       </c>
       <c r="B31">
@@ -2810,16 +2810,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ООО "Марс"</t>
+          <t>АО "ДКС"</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-5045016560 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-6905062011 от 21.04.26</t>
         </is>
       </c>
       <c r="E31">
-        <f>"LBO-LE-5045016560"</f>
+        <f>"LBO-LE-6905062011"</f>
         <v/>
       </c>
       <c r="F31" t="inlineStr">
@@ -2866,37 +2866,37 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=9dbf98c4-2f7d-449a-9c29-9ecc8113bed8&amp;documentId=7897fca0-d4e3-4186-8370-72f430726361</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=1db40d2f-58f6-4c1e-a1d8-db3112bdea1d&amp;documentId=d37df6e8-eb17-45ac-b66d-e0b8140e7c9a</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2BM-5045016560-2012101108055532096200000000000</t>
+          <t>2BM-6905062011-2012073010503125473850000000000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <f>"7707049388"</f>
+        <f>"9729292654"</f>
         <v/>
       </c>
       <c r="B32">
-        <f>"770545001"</f>
+        <f>"772901001"</f>
         <v/>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Корпоративный Центр ПАО «Ростелеком»</t>
+          <t>ООО "АДАПТИВНЫЕ ТЕХНОЛОГИИ РАЗВИТИЯ"</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7707049388 от 22.04.26</t>
+          <t>Доп. соглашение №LBO-LE-9729292654 от 22.04.26</t>
         </is>
       </c>
       <c r="E32">
-        <f>"LBO-LE-7707049388"</f>
+        <f>"LBO-LE-9729292654"</f>
         <v/>
       </c>
       <c r="F32" t="inlineStr">
@@ -2943,37 +2943,37 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=e0f4d7d5-8f4a-4338-abe5-a5895b4a67e5&amp;documentId=ab83c72b-ecee-4d2f-ae42-c0140aaabcd0</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=2c8edd22-c03c-4fb8-9584-ae2359e06387&amp;documentId=8dad496f-445c-452f-a592-4f4dc8abed59</t>
         </is>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2BM-7707049388-770545001-201607140635186717595</t>
+          <t>2BM-9729292654-772901001-202002050849418300734</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <f>"3812014066"</f>
+        <f>"7449006184"</f>
         <v/>
       </c>
       <c r="B33">
-        <f>"381201001"</f>
+        <f>"744901001"</f>
         <v/>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ИРНИТУ, ФГБОУ ВО "ИРНИТУ", "ИРКУТСКИЙ ПОЛИТЕХ"</t>
+          <t>ПАО ЧКПЗ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-3812014066 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7449006184 от 21.04.26</t>
         </is>
       </c>
       <c r="E33">
-        <f>"LBO-LE-3812014066"</f>
+        <f>"LBS-LE-7449006184"</f>
         <v/>
       </c>
       <c r="F33" t="inlineStr">
@@ -3020,37 +3020,37 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=acc434a3-c17e-4b1f-b91f-9e3d4b91dfeb&amp;documentId=36399ca7-465e-49a5-8f6b-d2de3424d969</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=70475ea8-a196-4591-a21e-2469772f72b6&amp;documentId=de2dece1-231d-4463-a3e3-91c94f085df7</t>
         </is>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2BM-3812014066-2012052808335486382630000000000</t>
+          <t>2BM-7449006184-2013021407202572705510000000000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <f>"9731026963"</f>
+        <f>"1901120231"</f>
         <v/>
       </c>
       <c r="B34">
-        <f>"773101001"</f>
+        <f>"190101001"</f>
         <v/>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ООО "СМАРТ КОНСТРАКШН"</t>
+          <t>ГАУ РХ "ЦИНТ ХАКАСИИ"</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9731026963 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-1901120231 от 21.04.26</t>
         </is>
       </c>
       <c r="E34">
-        <f>"LBO-LE-9731026963"</f>
+        <f>"LBS-LE-1901120231"</f>
         <v/>
       </c>
       <c r="F34" t="inlineStr">
@@ -3097,37 +3097,37 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=7c5bc887-5a0f-4d0b-a942-b1dbe8b0e05c&amp;documentId=104185aa-b428-47c2-a163-644803102afa</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0724112c-f0ab-47e6-8ebe-d3e5961222b5&amp;documentId=b7ef9b5f-fcef-46d2-b133-d457bc872e37</t>
         </is>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2BM-9731026963-773101001-201903050133339128614</t>
+          <t>2BM-1901120231-190101001-201601190100274509593</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <f>"7736249247"</f>
+        <f>"7811753424"</f>
         <v/>
       </c>
       <c r="B35">
-        <f>"773001001"</f>
+        <f>"781001001"</f>
         <v/>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ООО "ДОМКЛИК"</t>
+          <t>ООО "ОЗБЭТТЕРИЗ"</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7736249247 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7811753424 от 21.04.26</t>
         </is>
       </c>
       <c r="E35">
-        <f>"LBO-LE-7736249247"</f>
+        <f>"LBO-LE-7811753424"</f>
         <v/>
       </c>
       <c r="F35" t="inlineStr">
@@ -3174,42 +3174,42 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=3e8bf875-5b7c-4767-99fb-1b40a4a05719&amp;documentId=4801cc52-7954-44ef-b830-87c5afe61d97</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=144c8b91-e507-4a0b-b827-17068f1ee5fc&amp;documentId=bbbbc8f5-5a4c-40b5-adad-87aaf989d2c9</t>
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2BM-7736249247-773601001-201509281136356578567</t>
+          <t>2BM-7811753424-781101001-202101280852447862235</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <f>"7813286694"</f>
+        <f>"7717586110"</f>
         <v/>
       </c>
       <c r="B36">
-        <f>"781301001"</f>
+        <f>"770501001"</f>
         <v/>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ООО "МАИНД КРАФТ"</t>
+          <t>ООО "1С-Битрикс"</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7813286694 от 22.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7717586110 от 21.04.26</t>
         </is>
       </c>
       <c r="E36">
-        <f>"LBO-LE-7813286694"</f>
+        <f>"LBO-LE-7717586110"</f>
         <v/>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>22.04.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3251,37 +3251,37 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=65c7d854-9ff8-46a8-b12e-4561be01ec77&amp;documentId=f8e87405-0671-4a18-8188-474f63d81cdd</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=fb29d128-a8f3-49e0-b45d-6cc0247e2f33&amp;documentId=6db8b825-5d93-4467-8506-107415352063</t>
         </is>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2BM-7813286694-781301001-201808091253388026694</t>
+          <t>2BM-7717586110-2012052807532742374290000000000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <f>"1106010917"</f>
+        <f>"2225004738"</f>
         <v/>
       </c>
       <c r="B37">
-        <f>"771401001"</f>
+        <f>"222501001"</f>
         <v/>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ООО "АКС"</t>
+          <t>ФГБОУ ВО "АЛТАЙСКИЙ ГОСУДАРСТВЕННЫЙ УНИВЕРСИТЕТ",АЛТГУ,АЛТАЙСКИЙ ГОСУДАРСТВЕННЫЙ УНИВЕРСИТЕТ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-1106010917 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-2225004738 от 21.04.26</t>
         </is>
       </c>
       <c r="E37">
-        <f>"LBO-LE-1106010917"</f>
+        <f>"LBS-LE-2225004738"</f>
         <v/>
       </c>
       <c r="F37" t="inlineStr">
@@ -3301,7 +3301,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3312,7 +3312,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3328,37 +3328,37 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=97cf189a-9d0f-4baf-bac2-99f6f282ab5d&amp;documentId=d15bd043-2a7b-4418-bbfd-1b44e8b2deb9</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=cf3028fd-9483-493d-b8aa-2899c90f4caa&amp;documentId=d9ab08f7-938e-4d5c-ae06-7e95407043f4</t>
         </is>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2BM-1106010917-110601001-201506250750435011955</t>
+          <t>2BM-2225004738-2012052808173457542630000000000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <f>"7203518506"</f>
+        <f>"7736316133"</f>
         <v/>
       </c>
       <c r="B38">
-        <f>"720301001"</f>
+        <f>"771401001"</f>
         <v/>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ООО "СЛАЙДЕР ПРЕЗЕНТАЦИИ"</t>
+          <t>АНО "ШКОЛА 21"</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7203518506 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7736316133 от 21.04.26</t>
         </is>
       </c>
       <c r="E38">
-        <f>"LBO-LE-7203518506"</f>
+        <f>"LBS-LE-7736316133"</f>
         <v/>
       </c>
       <c r="F38" t="inlineStr">
@@ -3378,7 +3378,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3389,7 +3389,7 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3405,42 +3405,42 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=61218573-0e48-4151-a401-1ea87e35aa37&amp;documentId=a42f4a5b-0cbd-4a8e-8897-14a0ef1fa89b</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=5e7ec2c5-7521-49b3-8c3c-d9132ed3a7e9&amp;documentId=5c24e488-296b-4287-b028-0d0e83f46542</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2BM-7203518506-720301001-202205301005006799187</t>
+          <t>2BM-7736316133-773601001-201810181141010759818</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <f>"7708328948"</f>
+        <f>"7744002123"</f>
         <v/>
       </c>
       <c r="B39">
-        <f>"770801001"</f>
+        <f>"773001001"</f>
         <v/>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ООО "ЗВУК"</t>
+          <t>ООО СК "СБЕРБАНК СТРАХОВАНИЕ ЖИЗНИ"</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7708328948 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7744002123 от 22.04.26</t>
         </is>
       </c>
       <c r="E39">
-        <f>"LBO-LE-7708328948"</f>
+        <f>"LBS-LE-7744002123"</f>
         <v/>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3466,7 +3466,7 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=02cf6236-5056-4b1a-ac32-a813f2646409&amp;documentId=2cfaa4a1-9ed3-4e37-9177-641418b3a3a5</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=d12d8afc-056d-47c3-8002-c05afb5d588e&amp;documentId=7721357e-c329-440f-8035-52ffb08a4fe1</t>
         </is>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2BM-7708328948-770801001-201802150551001262544</t>
+          <t>2BK-7744002123-377762</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <f>"5047243826"</f>
+        <f>"9731065465"</f>
         <v/>
       </c>
       <c r="B40">
-        <f>"504701001"</f>
+        <f>"773101001"</f>
         <v/>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ООО "КД-СИСТЕМС"</t>
+          <t>ООО "СБЕРМЕДИИ"</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-5047243826 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-9731065465 от 21.04.26</t>
         </is>
       </c>
       <c r="E40">
-        <f>"LBO-LE-5047243826"</f>
+        <f>"LBO-LE-9731065465"</f>
         <v/>
       </c>
       <c r="F40" t="inlineStr">
@@ -3532,7 +3532,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3543,7 +3543,7 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3559,42 +3559,42 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=4700d11c-9eca-44c4-8636-a92e6c8092d3&amp;documentId=baa26fdb-3f35-49fe-bec8-0e65a3ac86fe</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=bf6924e7-71da-4323-8f6d-81bca3bcb9c3&amp;documentId=c4b1a76c-de5c-4fc1-87b9-69cc4738bafe</t>
         </is>
       </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2BM-5047243826-504701001-202011120905120310334</t>
+          <t>2BM-9731065465-773101001-202008251257056035458</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <f>"7736227885"</f>
+        <f>"2540022316"</f>
         <v/>
       </c>
       <c r="B41">
-        <f>"774950001"</f>
+        <f>"254001001"</f>
         <v/>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ПАО "СОФТЛАЙН"</t>
+          <t>ФГБУ "Приморское УГМС"</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7736227885 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-2540022316 от 22.04.26</t>
         </is>
       </c>
       <c r="E41">
-        <f>"LBO-LE-7736227885"</f>
+        <f>"LBS-LE-2540022316"</f>
         <v/>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -3609,7 +3609,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3620,7 +3620,7 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3636,37 +3636,37 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=d3fb0060-86fd-4be9-a622-a982e81e88d5&amp;documentId=ebbc9b66-2caa-4378-85d6-1f2efd5f85ea</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=a8f9013c-1f71-42a3-a86b-a0b375cfcc05&amp;documentId=b0b96332-fa3a-4cc5-8cfc-80a0ec3677f6</t>
         </is>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2BM-7736227885-2012052807543104095070000000000</t>
+          <t>2BM-2540022316-2013022203274380580680000000000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <f>"1615014289"</f>
+        <f>"3460062918"</f>
         <v/>
       </c>
       <c r="B42">
-        <f>"161501001"</f>
+        <f>"344401001"</f>
         <v/>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ООО "ИТ ИКС 5 ТЕХНОЛОГИИ"</t>
+          <t>ООО "ХЕППИВЕАР ЮГ"</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-1615014289 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-3460062918 от 21.04.26</t>
         </is>
       </c>
       <c r="E42">
-        <f>"LBO-LE-1615014289"</f>
+        <f>"LBO-LE-3460062918"</f>
         <v/>
       </c>
       <c r="F42" t="inlineStr">
@@ -3686,7 +3686,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3697,7 +3697,7 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3713,37 +3713,37 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=f21da06f-4fdc-4de5-8b57-c1223069eefe&amp;documentId=09556b58-ceb6-4608-818a-dc8fef8957d4</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=476672fa-2286-4a4e-bc9e-ef89d5c281e8&amp;documentId=1c073372-724b-475e-a4b2-0fe51ee8c49b</t>
         </is>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2BM-1615014289-161501001-201901211133246821673</t>
+          <t>2BM-3460062918-346001001-201701161254302210381</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <f>"7703435262"</f>
+        <f>"7714030726"</f>
         <v/>
       </c>
       <c r="B43">
-        <f>"772501001"</f>
+        <f>"770101001"</f>
         <v/>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ООО "РЭДМЭДРОБОТ МСК"</t>
+          <t>НАЦИОНАЛЬНЫЙ ИССЛЕДОВАТЕЛЬСКИЙ УНИВЕРСИТЕТ "ВЫСШАЯ ШКОЛА ЭКОНОМИКИ", НИУ "ВЫСШАЯ ШКОЛА ЭКОНОМИКИ", ВЫСШАЯ ШКОЛА ЭКОНОМИКИ, НИУ ВШЭ, ВШЭ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7703435262 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7714030726 от 21.04.26</t>
         </is>
       </c>
       <c r="E43">
-        <f>"LBO-LE-7703435262"</f>
+        <f>"LBS-LE-7714030726"</f>
         <v/>
       </c>
       <c r="F43" t="inlineStr">
@@ -3763,7 +3763,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3774,7 +3774,7 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3790,37 +3790,37 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=ac32a4e1-7f0b-4077-8322-5c689a2628fc&amp;documentId=5e0e00ef-3d29-4485-8fab-9dcf7f374a9b</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=a2b7363c-3a7b-4ed1-9db5-117dbb3939e4&amp;documentId=c8be2363-382e-4dd4-9327-e678b10a56f3</t>
         </is>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2BM-7703435262-770301001-201712180811074854645</t>
+          <t>2BM-7714030726-770101001-201403270404185229936</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <f>"5408130693"</f>
+        <f>"5045016560"</f>
         <v/>
       </c>
       <c r="B44">
-        <f>"997350001"</f>
+        <f>"997150001"</f>
         <v/>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>АО НПК "КАТРЕН"</t>
+          <t>ООО "Марс"</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-5408130693 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-5045016560 от 21.04.26</t>
         </is>
       </c>
       <c r="E44">
-        <f>"LBO-LE-5408130693"</f>
+        <f>"LBO-LE-5045016560"</f>
         <v/>
       </c>
       <c r="F44" t="inlineStr">
@@ -3840,7 +3840,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3851,7 +3851,7 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3867,42 +3867,42 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=28afdb72-0e51-4d63-bc8a-8949714517fa&amp;documentId=3b1b852c-f25a-4e96-8559-93d091ce88a8</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=9dbf98c4-2f7d-449a-9c29-9ecc8113bed8&amp;documentId=7897fca0-d4e3-4186-8370-72f430726361</t>
         </is>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2BM-5408130693-2012052807483620086810000000000</t>
+          <t>2BM-5045016560-2012101108055532096200000000000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <f>"7839438486"</f>
+        <f>"7707049388"</f>
         <v/>
       </c>
       <c r="B45">
-        <f>"780201001"</f>
+        <f>"770545001"</f>
         <v/>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ООО "ЦРТ-инновации"</t>
+          <t>Корпоративный Центр ПАО «Ростелеком»</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7839438486 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7707049388 от 22.04.26</t>
         </is>
       </c>
       <c r="E45">
-        <f>"LBO-LE-7839438486"</f>
+        <f>"LBO-LE-7707049388"</f>
         <v/>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -3917,7 +3917,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3928,7 +3928,7 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3944,37 +3944,37 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=33aff07c-db41-4461-bdec-9a496609515f&amp;documentId=22496147-ca1c-49b9-b332-3e8dc8f56188</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=e0f4d7d5-8f4a-4338-abe5-a5895b4a67e5&amp;documentId=ab83c72b-ecee-4d2f-ae42-c0140aaabcd0</t>
         </is>
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2BM-7839438486-783901001-201603160113040841825</t>
+          <t>2BM-7707049388-770545001-201607140635186717595</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <f>"1835056809"</f>
+        <f>"7811701440"</f>
         <v/>
       </c>
       <c r="B46">
-        <f>"184001001"</f>
+        <f>"781101001"</f>
         <v/>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ООО "ДИРЕКТУМ"</t>
+          <t>БФ "ЧЕСТЬ ИМЕЮ"</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-1835056809 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7811701440 от 21.04.26</t>
         </is>
       </c>
       <c r="E46">
-        <f>"LBO-LE-1835056809"</f>
+        <f>"LBS-LE-7811701440"</f>
         <v/>
       </c>
       <c r="F46" t="inlineStr">
@@ -3994,7 +3994,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4005,7 +4005,7 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4021,37 +4021,37 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=ad48981f-3dfa-4d6e-8c09-88a457f694d3&amp;documentId=f74b5e84-ae72-40f6-826a-7e9b89cfa104</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=6eb89f75-f33d-4da8-a8bf-912bd606503b&amp;documentId=7a6f607e-1d97-49e2-ab10-b0dbd6e7a96c</t>
         </is>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2BM-1835056809-184001001-202110091026132627344</t>
+          <t>2BM-7811701440-781101001-202409121050486401082</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <f>"7702609477"</f>
+        <f>"3812014066"</f>
         <v/>
       </c>
       <c r="B47">
-        <f>"774301001"</f>
+        <f>"381201001"</f>
         <v/>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ООО "ЮНИСТАР ДИДЖИТАЛ"</t>
+          <t>ИРНИТУ, ФГБОУ ВО "ИРНИТУ", "ИРКУТСКИЙ ПОЛИТЕХ"</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7702609477 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-3812014066 от 21.04.26</t>
         </is>
       </c>
       <c r="E47">
-        <f>"LBO-LE-7702609477"</f>
+        <f>"LBO-LE-3812014066"</f>
         <v/>
       </c>
       <c r="F47" t="inlineStr">
@@ -4071,7 +4071,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4082,7 +4082,7 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4098,37 +4098,37 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=cc34e782-c544-4989-a1c5-cd71f6a24e54&amp;documentId=efaeeff6-1b68-4e15-85b2-5bddf9892ca0</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=acc434a3-c17e-4b1f-b91f-9e3d4b91dfeb&amp;documentId=36399ca7-465e-49a5-8f6b-d2de3424d969</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2BM-7702609477-2013022203142863982470000000000</t>
+          <t>2BM-3812014066-2012052808335486382630000000000</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <f>"7725745476"</f>
+        <f>"6662005668"</f>
         <v/>
       </c>
       <c r="B48">
-        <f>"772501001"</f>
+        <f>"668501001"</f>
         <v/>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ООО "Живой Сайт"</t>
+          <t>ФБУ "УРАЛТЕСТ"</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7725745476 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-6662005668 от 21.04.26</t>
         </is>
       </c>
       <c r="E48">
-        <f>"LBO-LE-7725745476"</f>
+        <f>"LBS-LE-6662005668"</f>
         <v/>
       </c>
       <c r="F48" t="inlineStr">
@@ -4148,7 +4148,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4159,7 +4159,7 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4175,37 +4175,37 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0b538d0b-e8a1-48a0-9ca9-465ddf205cf6&amp;documentId=9c452848-2a71-4064-8c6e-667e3220dadd</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0d2a7233-f040-493c-8ca4-cf74fa485e9d&amp;documentId=e1e4c8a1-6ad4-4cbe-af9a-6aa910c760d3</t>
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2BM-7725745476-2012100101543217793580000000000</t>
+          <t>2BM-6662005668-2012052808351829262630000000000</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <f>"7702596813"</f>
+        <f>"7724890784"</f>
         <v/>
       </c>
       <c r="B49">
-        <f>"390601001"</f>
+        <f>"774950001"</f>
         <v/>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ООО "Бауцентр Рус"</t>
+          <t>АО "ОРМАТЕК"</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7702596813 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7724890784 от 21.04.26</t>
         </is>
       </c>
       <c r="E49">
-        <f>"LBO-LE-7702596813"</f>
+        <f>"LBS-LE-7724890784"</f>
         <v/>
       </c>
       <c r="F49" t="inlineStr">
@@ -4225,7 +4225,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4236,7 +4236,7 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4252,37 +4252,37 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=6b3acb60-c91c-4b56-981b-ab967e41e922&amp;documentId=d30c6f26-2ed1-499d-96a4-f04236f5b5bf</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=b4d90e56-c67d-4b09-8abd-676a321cb414&amp;documentId=4be71e90-11e0-4daa-b759-7391ef3bb6e4</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2BM-7702596813-2012052807321437821080000000000</t>
+          <t>2BM-7724890784-2013112512183967040250000000000</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <f>"6320075951"</f>
+        <f>"9731026963"</f>
         <v/>
       </c>
       <c r="B50">
-        <f>"632001001"</f>
+        <f>"773101001"</f>
         <v/>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ООО "РУТКОД АЙТИ ДЕВЕЛОПМЕНТ"</t>
+          <t>ООО "СМАРТ КОНСТРАКШН"</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-6320075951 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-9731026963 от 21.04.26</t>
         </is>
       </c>
       <c r="E50">
-        <f>"LBO-LE-6320075951"</f>
+        <f>"LBO-LE-9731026963"</f>
         <v/>
       </c>
       <c r="F50" t="inlineStr">
@@ -4302,7 +4302,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4313,7 +4313,7 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4329,37 +4329,37 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=55a070a1-67cc-4ffa-89cf-3852dd3cab82&amp;documentId=4f6856d2-a450-46e6-a617-44f3777b8a63</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=7c5bc887-5a0f-4d0b-a942-b1dbe8b0e05c&amp;documentId=104185aa-b428-47c2-a163-644803102afa</t>
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2BM-6320075951-632001001-202308080848322867126</t>
+          <t>2BM-9731026963-773101001-201903050133339128614</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <f>"7709969870"</f>
+        <f>"7736249247"</f>
         <v/>
       </c>
       <c r="B51">
-        <f>"770901001"</f>
+        <f>"773001001"</f>
         <v/>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ООО "РДВ-СОФТ"</t>
+          <t>ООО "ДОМКЛИК"</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7709969870 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7736249247 от 21.04.26</t>
         </is>
       </c>
       <c r="E51">
-        <f>"LBO-LE-7709969870"</f>
+        <f>"LBO-LE-7736249247"</f>
         <v/>
       </c>
       <c r="F51" t="inlineStr">
@@ -4379,7 +4379,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4390,7 +4390,7 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4406,42 +4406,42 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=fffcedeb-d9ea-4ef7-83b8-f528b9e902b2&amp;documentId=baea60e1-9b24-4764-9911-3a1c33af99d7</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=3e8bf875-5b7c-4767-99fb-1b40a4a05719&amp;documentId=4801cc52-7954-44ef-b830-87c5afe61d97</t>
         </is>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2BM-7709969870-770901001-201606300436327193051</t>
+          <t>2BM-7736249247-773601001-201509281136356578567</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <f>"9709054813"</f>
+        <f>"7813286694"</f>
         <v/>
       </c>
       <c r="B52">
-        <f>"771401001"</f>
+        <f>"781301001"</f>
         <v/>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ООО "СБЕРАВТО"</t>
+          <t>ООО "МАИНД КРАФТ"</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9709054813 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7813286694 от 22.04.26</t>
         </is>
       </c>
       <c r="E52">
-        <f>"LBO-LE-9709054813"</f>
+        <f>"LBO-LE-7813286694"</f>
         <v/>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -4456,7 +4456,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4467,7 +4467,7 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:17</t>
+          <t>22.04.2026 15:08:14</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4483,37 +4483,37 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0964e641-2fa1-4e4d-b529-1d7b00e26280&amp;documentId=42bdd24a-6305-45d0-a922-ac59d38316ea</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=65c7d854-9ff8-46a8-b12e-4561be01ec77&amp;documentId=f8e87405-0671-4a18-8188-474f63d81cdd</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2BM-9709054813-770901001-201911270307241702695</t>
+          <t>2BM-7813286694-781301001-201808091253388026694</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <f>"9705118142"</f>
+        <f>"5045073872"</f>
         <v/>
       </c>
       <c r="B53">
-        <f>"775101001"</f>
+        <f>"504501001"</f>
         <v/>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ООО "ИНСТАМАРТ СЕРВИС"</t>
+          <t>ООО "АЙТИМЕДИКА"</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9705118142 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-5045073872 от 21.04.26</t>
         </is>
       </c>
       <c r="E53">
-        <f>"LBO-LE-9705118142"</f>
+        <f>"LBS-LE-5045073872"</f>
         <v/>
       </c>
       <c r="F53" t="inlineStr">
@@ -4560,37 +4560,37 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=7ae6dcdb-7528-4fec-bac9-9f468e9a1308&amp;documentId=774cfa72-9e67-498c-97a3-645f4c99cdd5</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=350da484-3946-4e09-9466-c73f209ec2e0&amp;documentId=4d15852c-ccf5-4c2e-bbfc-9ddd01fe0ea8</t>
         </is>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2BM-9705118142-770501001-201808140708520629143</t>
+          <t>2BM-5045073872-504501001-202505240510515202357</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <f>"9709067058"</f>
+        <f>"6662005668"</f>
         <v/>
       </c>
       <c r="B54">
-        <f>"770901001"</f>
+        <f>"668501001"</f>
         <v/>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ООО "ГЛОУБАЙТ СОФТ"</t>
+          <t>ФБУ "УРАЛТЕСТ"</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9709067058 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-6662005668 от 21.04.26</t>
         </is>
       </c>
       <c r="E54">
-        <f>"LBO-LE-9709067058"</f>
+        <f>"LBS-LE-6662005668"</f>
         <v/>
       </c>
       <c r="F54" t="inlineStr">
@@ -4637,37 +4637,37 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=75916242-992b-4650-8921-40c2918ceae8&amp;documentId=613a91d2-d610-4c2a-a3c9-defd3de421d5</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=27b69916-4f16-41de-b680-6330b1008438&amp;documentId=0e78d192-d36a-499f-a074-043431fce192</t>
         </is>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2BM-9709067058-770901001-202012250802102617947</t>
+          <t>2BM-6662005668-2012052808351829262630000000000</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <f>"1657203961"</f>
+        <f>"1106010917"</f>
         <v/>
       </c>
       <c r="B55">
-        <f>"168301001"</f>
+        <f>"771401001"</f>
         <v/>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ООО "ИМПЛЕКС"</t>
+          <t>ООО "АКС"</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-1657203961 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-1106010917 от 21.04.26</t>
         </is>
       </c>
       <c r="E55">
-        <f>"LBO-LE-1657203961"</f>
+        <f>"LBO-LE-1106010917"</f>
         <v/>
       </c>
       <c r="F55" t="inlineStr">
@@ -4687,7 +4687,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:20</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4698,7 +4698,7 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:20</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -4714,37 +4714,37 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=4577a335-3abe-4a26-a414-99ea818841a7&amp;documentId=fdeda9a2-002e-4b10-929d-5b4f31d1be13</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=97cf189a-9d0f-4baf-bac2-99f6f282ab5d&amp;documentId=d15bd043-2a7b-4418-bbfd-1b44e8b2deb9</t>
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2BM-1657203961-165701001-201608040756542710551</t>
+          <t>2BM-1106010917-110601001-201506250750435011955</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <f>"7736319695"</f>
+        <f>"7203518506"</f>
         <v/>
       </c>
       <c r="B56">
-        <f>"773601001"</f>
+        <f>"720301001"</f>
         <v/>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ООО "С-МАРКЕТИНГ"</t>
+          <t>ООО "СЛАЙДЕР ПРЕЗЕНТАЦИИ"</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7736319695 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7203518506 от 21.04.26</t>
         </is>
       </c>
       <c r="E56">
-        <f>"LBO-LE-7736319695"</f>
+        <f>"LBO-LE-7203518506"</f>
         <v/>
       </c>
       <c r="F56" t="inlineStr">
@@ -4764,7 +4764,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:20</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4775,7 +4775,7 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>22.04.2026 15:08:20</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4791,37 +4791,37 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=2bcfa11b-5d4f-4fee-a89c-81354f1ffdee&amp;documentId=8d343abe-28f0-4fc4-87af-d64b6537841c</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=61218573-0e48-4151-a401-1ea87e35aa37&amp;documentId=a42f4a5b-0cbd-4a8e-8897-14a0ef1fa89b</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2BM-7736319695-773601001-201907310301149591624</t>
+          <t>2BM-7203518506-720301001-202205301005006799187</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <f>"7805093681"</f>
+        <f>"7728312865"</f>
         <v/>
       </c>
       <c r="B57">
-        <f>"997750001"</f>
+        <f>"772801001"</f>
         <v/>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ООО "ЦРТ"</t>
+          <t>ООО "АСТ ГОЗ"</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7805093681 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-7728312865 от 21.04.26</t>
         </is>
       </c>
       <c r="E57">
-        <f>"LBO-LE-7805093681"</f>
+        <f>"LBS-LE-7728312865"</f>
         <v/>
       </c>
       <c r="F57" t="inlineStr">
@@ -4841,7 +4841,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4852,7 +4852,7 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -4868,37 +4868,37 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=72bb46b0-2be9-4ddb-aec2-21b15b953c2a&amp;documentId=9e796057-2927-49cd-b2b6-d851dc45f185</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=8ab99c23-d42c-43d7-b3ab-bd05af1bf735&amp;documentId=a1df1d64-bcff-4592-9e0d-b5319547ad55</t>
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2BM-7805093681-783901001-201408081114163414308</t>
+          <t>2BM-7728312865-772801001-201511250720572730102</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <f>"7736128605"</f>
+        <f>"7708328948"</f>
         <v/>
       </c>
       <c r="B58">
-        <f>"773601001"</f>
+        <f>"770801001"</f>
         <v/>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>АНО ДПО "КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА", КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА, СБЕРУНИВЕРСИТЕТ</t>
+          <t>ООО "ЗВУК"</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7736128605 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7708328948 от 21.04.26</t>
         </is>
       </c>
       <c r="E58">
-        <f>"LBO-LE-7736128605"</f>
+        <f>"LBO-LE-7708328948"</f>
         <v/>
       </c>
       <c r="F58" t="inlineStr">
@@ -4918,7 +4918,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4929,7 +4929,7 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -4945,37 +4945,37 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=effd6672-3f8c-4f95-be1e-cd4ece30e501&amp;documentId=bd40a11c-3e82-4e2d-a270-c1302c371b98</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=02cf6236-5056-4b1a-ac32-a813f2646409&amp;documentId=2cfaa4a1-9ed3-4e37-9177-641418b3a3a5</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2BM-7736128605-773601001-201603211141413966693</t>
+          <t>2BM-7708328948-770801001-201802150551001262544</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <f>"7736279160"</f>
+        <f>"5047243826"</f>
         <v/>
       </c>
       <c r="B59">
-        <f>"997750001"</f>
+        <f>"504701001"</f>
         <v/>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ООО "ОБЛАЧНЫЕ ТЕХНОЛОГИИ"</t>
+          <t>ООО "КД-СИСТЕМС"</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7736279160 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-5047243826 от 21.04.26</t>
         </is>
       </c>
       <c r="E59">
-        <f>"LBO-LE-7736279160"</f>
+        <f>"LBO-LE-5047243826"</f>
         <v/>
       </c>
       <c r="F59" t="inlineStr">
@@ -4995,7 +4995,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5006,7 +5006,7 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5022,37 +5022,37 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=2639f91a-34cd-4587-aa58-81fcbbba8e9b&amp;documentId=c03c5f96-28f0-46f0-bace-1de817906394</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=4700d11c-9eca-44c4-8636-a92e6c8092d3&amp;documentId=baa26fdb-3f35-49fe-bec8-0e65a3ac86fe</t>
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2BM-7736279160-773601001-201701251001477042849</t>
+          <t>2BM-5047243826-504701001-202011120905120310334</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <f>"7715995942"</f>
+        <f>"7736227885"</f>
         <v/>
       </c>
       <c r="B60">
-        <f>"770701001"</f>
+        <f>"774950001"</f>
         <v/>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>АО "ИЗДАТЕЛЬСТВО "ПРОСВЕЩЕНИЕ"</t>
+          <t>ПАО "СОФТЛАЙН"</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7715995942 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7736227885 от 21.04.26</t>
         </is>
       </c>
       <c r="E60">
-        <f>"LBO-LE-7715995942"</f>
+        <f>"LBO-LE-7736227885"</f>
         <v/>
       </c>
       <c r="F60" t="inlineStr">
@@ -5072,7 +5072,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5083,7 +5083,7 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5099,37 +5099,37 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=4b1f8c5b-fc86-47d9-a538-eb8b2d1dbe3d&amp;documentId=7ed7afdb-fca7-4ba1-9c10-3b1c91583ce2</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=d3fb0060-86fd-4be9-a622-a982e81e88d5&amp;documentId=ebbc9b66-2caa-4378-85d6-1f2efd5f85ea</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2BM-7715995942-771501001-201404070308335649912</t>
+          <t>2BM-7736227885-2012052807543104095070000000000</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <f>"7704017596"</f>
+        <f>"1615014289"</f>
         <v/>
       </c>
       <c r="B61">
-        <f>"997150001"</f>
+        <f>"161501001"</f>
         <v/>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>АО "БАЙЕР"</t>
+          <t>ООО "ИТ ИКС 5 ТЕХНОЛОГИИ"</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7704017596 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-1615014289 от 21.04.26</t>
         </is>
       </c>
       <c r="E61">
-        <f>"LBO-LE-7704017596"</f>
+        <f>"LBO-LE-1615014289"</f>
         <v/>
       </c>
       <c r="F61" t="inlineStr">
@@ -5149,7 +5149,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5160,7 +5160,7 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5176,37 +5176,37 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=6f22bc06-97b1-4ebe-897b-12f3d1f0fd92&amp;documentId=9f0a1f0b-a2b9-435e-94dc-4ec81a92d390</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=f21da06f-4fdc-4de5-8b57-c1223069eefe&amp;documentId=09556b58-ceb6-4608-818a-dc8fef8957d4</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2BM-7704017596-2012052808233697902630000000000</t>
+          <t>2BM-1615014289-161501001-201901211133246821673</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <f>"9715347247"</f>
+        <f>"7703435262"</f>
         <v/>
       </c>
       <c r="B62">
-        <f>"770501001"</f>
+        <f>"772501001"</f>
         <v/>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ООО "РОБОВОЙС"</t>
+          <t>ООО "РЭДМЭДРОБОТ МСК"</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-9715347247 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7703435262 от 21.04.26</t>
         </is>
       </c>
       <c r="E62">
-        <f>"LBO-LE-9715347247"</f>
+        <f>"LBO-LE-7703435262"</f>
         <v/>
       </c>
       <c r="F62" t="inlineStr">
@@ -5226,7 +5226,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5237,7 +5237,7 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5253,37 +5253,37 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0f8ed590-3003-4783-a909-416dbb357e07&amp;documentId=7f990545-31f3-413f-8618-c17ab103de4f</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=ac32a4e1-7f0b-4077-8322-5c689a2628fc&amp;documentId=5e0e00ef-3d29-4485-8fab-9dcf7f374a9b</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2BM-9715347247-771501001-201906101102562235725</t>
+          <t>2BM-7703435262-770301001-201712180811074854645</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <f>"7702019950"</f>
+        <f>"5408130693"</f>
         <v/>
       </c>
       <c r="B63">
-        <f>"771401001"</f>
+        <f>"997350001"</f>
         <v/>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>АО "КЭПТ"</t>
+          <t>АО НПК "КАТРЕН"</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7702019950 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-5408130693 от 21.04.26</t>
         </is>
       </c>
       <c r="E63">
-        <f>"LBO-LE-7702019950"</f>
+        <f>"LBO-LE-5408130693"</f>
         <v/>
       </c>
       <c r="F63" t="inlineStr">
@@ -5303,7 +5303,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5330,37 +5330,37 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=42ce06a2-1b55-4c65-a27b-06870c9c2fbd&amp;documentId=a6e8e62e-2f7e-46e4-9922-d30bab2ec961</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=28afdb72-0e51-4d63-bc8a-8949714517fa&amp;documentId=3b1b852c-f25a-4e96-8559-93d091ce88a8</t>
         </is>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2BM-7702019950-2013022203370240223770000000000</t>
+          <t>2BM-5408130693-2012052807483620086810000000000</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <f>"7736128605"</f>
+        <f>"7839438486"</f>
         <v/>
       </c>
       <c r="B64">
-        <f>"773601001"</f>
+        <f>"780201001"</f>
         <v/>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>АНО ДПО "КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА", КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА, СБЕРУНИВЕРСИТЕТ</t>
+          <t>ООО "ЦРТ-инновации"</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7736128605 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7839438486 от 21.04.26</t>
         </is>
       </c>
       <c r="E64">
-        <f>"LBO-LE-7736128605"</f>
+        <f>"LBO-LE-7839438486"</f>
         <v/>
       </c>
       <c r="F64" t="inlineStr">
@@ -5380,7 +5380,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5391,7 +5391,7 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -5407,37 +5407,37 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=da31b4ba-962d-4a7a-91ac-b0588be62dfd&amp;documentId=e122fe1a-f890-46e6-b6c5-bbffcf42c248</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=33aff07c-db41-4461-bdec-9a496609515f&amp;documentId=22496147-ca1c-49b9-b332-3e8dc8f56188</t>
         </is>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2BM-7736128605-773601001-201603211141413966693</t>
+          <t>2BM-7839438486-783901001-201603160113040841825</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <f>"7736128605"</f>
+        <f>"1835056809"</f>
         <v/>
       </c>
       <c r="B65">
-        <f>"773601001"</f>
+        <f>"184001001"</f>
         <v/>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>АНО ДПО "КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА", КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА, СБЕРУНИВЕРСИТЕТ</t>
+          <t>ООО "ДИРЕКТУМ"</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7736128605 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-1835056809 от 21.04.26</t>
         </is>
       </c>
       <c r="E65">
-        <f>"LBO-LE-7736128605"</f>
+        <f>"LBO-LE-1835056809"</f>
         <v/>
       </c>
       <c r="F65" t="inlineStr">
@@ -5457,7 +5457,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5468,7 +5468,7 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>22.04.2026 15:09:00</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -5484,37 +5484,37 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=8fcbde8c-a54b-4aa8-b1fc-8f347506da06&amp;documentId=5fe84401-17ba-4796-be79-25c84ee55233</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=ad48981f-3dfa-4d6e-8c09-88a457f694d3&amp;documentId=f74b5e84-ae72-40f6-826a-7e9b89cfa104</t>
         </is>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2BM-7736128605-773601001-201603211141413966693</t>
+          <t>2BM-1835056809-184001001-202110091026132627344</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <f>"7730269550"</f>
+        <f>"7702609477"</f>
         <v/>
       </c>
       <c r="B66">
-        <f>"773001001"</f>
+        <f>"774301001"</f>
         <v/>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ООО "СБЕР БИЗНЕС СОФТ"</t>
+          <t>ООО "ЮНИСТАР ДИДЖИТАЛ"</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7730269550 от 21.04.26</t>
+          <t>Доп. соглашение №LBO-LE-7702609477 от 21.04.26</t>
         </is>
       </c>
       <c r="E66">
-        <f>"LBO-LE-7730269550"</f>
+        <f>"LBO-LE-7702609477"</f>
         <v/>
       </c>
       <c r="F66" t="inlineStr">
@@ -5532,16 +5532,20 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Требуется подписать и отправить</t>
+          <t>Ожидается промежуточная подпись</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>21.04.2026 18:21:23</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -5557,37 +5561,42 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=29bfe4ac-ee45-4a7c-a0a6-3706a6313fe1&amp;documentId=1ef45b11-331d-4c00-a460-f941e0241378</t>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=cc34e782-c544-4989-a1c5-cd71f6a24e54&amp;documentId=efaeeff6-1b68-4e15-85b2-5bddf9892ca0</t>
         </is>
       </c>
       <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2BM-7702609477-2013022203142863982470000000000</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
-        <f>"7750005725"</f>
+        <f>"6671094142"</f>
         <v/>
       </c>
       <c r="B67">
-        <f>"770501001"</f>
+        <f>"667101001"</f>
         <v/>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ООО НКО "ЮМАНИ"</t>
+          <t>ООО "ПСС"</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Доп. соглашение №LBO-LE-7750005725 от 21.04.26</t>
+          <t>Доп. соглашение №LBS-LE-6671094142 от 22.04.26</t>
         </is>
       </c>
       <c r="E67">
-        <f>"LBO-LE-7750005725"</f>
+        <f>"LBS-LE-6671094142"</f>
         <v/>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -5600,16 +5609,20 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Требуется подписать и отправить</t>
+          <t>Ожидается промежуточная подпись</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>21.04.2026 19:16:56</t>
+          <t>22.04.2026 15:08:17</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -5625,13 +5638,1694 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=695da56c-3d67-47bc-be05-f1c8fc4ed654&amp;documentId=52df72d7-6488-49d5-9ca7-f7b0380ccace</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2BM-6671094142-667101001-202006220611397997902</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <f>"7725745476"</f>
+        <v/>
+      </c>
+      <c r="B68">
+        <f>"772501001"</f>
+        <v/>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ООО "Живой Сайт"</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7725745476 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E68">
+        <f>"LBO-LE-7725745476"</f>
+        <v/>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0b538d0b-e8a1-48a0-9ca9-465ddf205cf6&amp;documentId=9c452848-2a71-4064-8c6e-667e3220dadd</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2BM-7725745476-2012100101543217793580000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <f>"7702596813"</f>
+        <v/>
+      </c>
+      <c r="B69">
+        <f>"390601001"</f>
+        <v/>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ООО "Бауцентр Рус"</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7702596813 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E69">
+        <f>"LBO-LE-7702596813"</f>
+        <v/>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=6b3acb60-c91c-4b56-981b-ab967e41e922&amp;documentId=d30c6f26-2ed1-499d-96a4-f04236f5b5bf</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2BM-7702596813-2012052807321437821080000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <f>"6320075951"</f>
+        <v/>
+      </c>
+      <c r="B70">
+        <f>"632001001"</f>
+        <v/>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ООО "РУТКОД АЙТИ ДЕВЕЛОПМЕНТ"</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-6320075951 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E70">
+        <f>"LBO-LE-6320075951"</f>
+        <v/>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=55a070a1-67cc-4ffa-89cf-3852dd3cab82&amp;documentId=4f6856d2-a450-46e6-a617-44f3777b8a63</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2BM-6320075951-632001001-202308080848322867126</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <f>"7707308480"</f>
+        <v/>
+      </c>
+      <c r="B71">
+        <f>"770401001"</f>
+        <v/>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>АО "СБЕРБАНК - АСТ"</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBS-LE-7707308480 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E71">
+        <f>"LBS-LE-7707308480"</f>
+        <v/>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=fc15a183-3893-450f-a504-a24755777905&amp;documentId=07be06e7-15b1-463a-abd7-17f41cd6360b</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2BM-7707308480-2012052808134172982630000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <f>"7709969870"</f>
+        <v/>
+      </c>
+      <c r="B72">
+        <f>"770901001"</f>
+        <v/>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ООО "РДВ-СОФТ"</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7709969870 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E72">
+        <f>"LBO-LE-7709969870"</f>
+        <v/>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=fffcedeb-d9ea-4ef7-83b8-f528b9e902b2&amp;documentId=baea60e1-9b24-4764-9911-3a1c33af99d7</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2BM-7709969870-770901001-201606300436327193051</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <f>"1655258235"</f>
+        <v/>
+      </c>
+      <c r="B73">
+        <f>"161501001"</f>
+        <v/>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>АНО ВО "УНИВЕРСИТЕТ ИННОПОЛИС"</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBS-LE-1655258235 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E73">
+        <f>"LBS-LE-1655258235"</f>
+        <v/>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=f91cebb8-2a3a-4046-9eff-d654e392e13c&amp;documentId=c58aa227-9f5b-4853-86ec-95c7ad79be38</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2BM-1655258235-165501001-201410290241533874121</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <f>"9709054813"</f>
+        <v/>
+      </c>
+      <c r="B74">
+        <f>"771401001"</f>
+        <v/>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ООО "СБЕРАВТО"</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-9709054813 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E74">
+        <f>"LBO-LE-9709054813"</f>
+        <v/>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0964e641-2fa1-4e4d-b529-1d7b00e26280&amp;documentId=42bdd24a-6305-45d0-a922-ac59d38316ea</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2BM-9709054813-770901001-201911270307241702695</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <f>"9705118142"</f>
+        <v/>
+      </c>
+      <c r="B75">
+        <f>"775101001"</f>
+        <v/>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ООО "ИНСТАМАРТ СЕРВИС"</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-9705118142 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E75">
+        <f>"LBO-LE-9705118142"</f>
+        <v/>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=7ae6dcdb-7528-4fec-bac9-9f468e9a1308&amp;documentId=774cfa72-9e67-498c-97a3-645f4c99cdd5</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2BM-9705118142-770501001-201808140708520629143</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <f>"9709067058"</f>
+        <v/>
+      </c>
+      <c r="B76">
+        <f>"770901001"</f>
+        <v/>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ООО "ГЛОУБАЙТ СОФТ"</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-9709067058 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E76">
+        <f>"LBO-LE-9709067058"</f>
+        <v/>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:17</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=75916242-992b-4650-8921-40c2918ceae8&amp;documentId=613a91d2-d610-4c2a-a3c9-defd3de421d5</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2BM-9709067058-770901001-202012250802102617947</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <f>"1657203961"</f>
+        <v/>
+      </c>
+      <c r="B77">
+        <f>"168301001"</f>
+        <v/>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ООО "ИМПЛЕКС"</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-1657203961 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E77">
+        <f>"LBO-LE-1657203961"</f>
+        <v/>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:20</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:20</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=4577a335-3abe-4a26-a414-99ea818841a7&amp;documentId=fdeda9a2-002e-4b10-929d-5b4f31d1be13</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2BM-1657203961-165701001-201608040756542710551</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <f>"7736319695"</f>
+        <v/>
+      </c>
+      <c r="B78">
+        <f>"773601001"</f>
+        <v/>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ООО "С-МАРКЕТИНГ"</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7736319695 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E78">
+        <f>"LBO-LE-7736319695"</f>
+        <v/>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:20</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:08:20</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=2bcfa11b-5d4f-4fee-a89c-81354f1ffdee&amp;documentId=8d343abe-28f0-4fc4-87af-d64b6537841c</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2BM-7736319695-773601001-201907310301149591624</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <f>"7805093681"</f>
+        <v/>
+      </c>
+      <c r="B79">
+        <f>"997750001"</f>
+        <v/>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ООО "ЦРТ"</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7805093681 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E79">
+        <f>"LBO-LE-7805093681"</f>
+        <v/>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=72bb46b0-2be9-4ddb-aec2-21b15b953c2a&amp;documentId=9e796057-2927-49cd-b2b6-d851dc45f185</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2BM-7805093681-783901001-201408081114163414308</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <f>"7736128605"</f>
+        <v/>
+      </c>
+      <c r="B80">
+        <f>"773601001"</f>
+        <v/>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>АНО ДПО "КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА", КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА, СБЕРУНИВЕРСИТЕТ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7736128605 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E80">
+        <f>"LBO-LE-7736128605"</f>
+        <v/>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=effd6672-3f8c-4f95-be1e-cd4ece30e501&amp;documentId=bd40a11c-3e82-4e2d-a270-c1302c371b98</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2BM-7736128605-773601001-201603211141413966693</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <f>"7736279160"</f>
+        <v/>
+      </c>
+      <c r="B81">
+        <f>"997750001"</f>
+        <v/>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ООО "ОБЛАЧНЫЕ ТЕХНОЛОГИИ"</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7736279160 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E81">
+        <f>"LBO-LE-7736279160"</f>
+        <v/>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=2639f91a-34cd-4587-aa58-81fcbbba8e9b&amp;documentId=c03c5f96-28f0-46f0-bace-1de817906394</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2BM-7736279160-773601001-201701251001477042849</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <f>"7715995942"</f>
+        <v/>
+      </c>
+      <c r="B82">
+        <f>"770701001"</f>
+        <v/>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>АО "ИЗДАТЕЛЬСТВО "ПРОСВЕЩЕНИЕ"</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7715995942 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E82">
+        <f>"LBO-LE-7715995942"</f>
+        <v/>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=4b1f8c5b-fc86-47d9-a538-eb8b2d1dbe3d&amp;documentId=7ed7afdb-fca7-4ba1-9c10-3b1c91583ce2</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2BM-7715995942-771501001-201404070308335649912</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <f>"7704017596"</f>
+        <v/>
+      </c>
+      <c r="B83">
+        <f>"997150001"</f>
+        <v/>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>АО "БАЙЕР"</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7704017596 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E83">
+        <f>"LBO-LE-7704017596"</f>
+        <v/>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=6f22bc06-97b1-4ebe-897b-12f3d1f0fd92&amp;documentId=9f0a1f0b-a2b9-435e-94dc-4ec81a92d390</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2BM-7704017596-2012052808233697902630000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <f>"9715347247"</f>
+        <v/>
+      </c>
+      <c r="B84">
+        <f>"770501001"</f>
+        <v/>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ООО "РОБОВОЙС"</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-9715347247 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E84">
+        <f>"LBO-LE-9715347247"</f>
+        <v/>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=0f8ed590-3003-4783-a909-416dbb357e07&amp;documentId=7f990545-31f3-413f-8618-c17ab103de4f</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2BM-9715347247-771501001-201906101102562235725</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <f>"7702019950"</f>
+        <v/>
+      </c>
+      <c r="B85">
+        <f>"771401001"</f>
+        <v/>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>АО "КЭПТ"</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7702019950 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E85">
+        <f>"LBO-LE-7702019950"</f>
+        <v/>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=42ce06a2-1b55-4c65-a27b-06870c9c2fbd&amp;documentId=a6e8e62e-2f7e-46e4-9922-d30bab2ec961</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2BM-7702019950-2013022203370240223770000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <f>"7736128605"</f>
+        <v/>
+      </c>
+      <c r="B86">
+        <f>"773601001"</f>
+        <v/>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>АНО ДПО "КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА", КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА, СБЕРУНИВЕРСИТЕТ</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7736128605 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E86">
+        <f>"LBO-LE-7736128605"</f>
+        <v/>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=da31b4ba-962d-4a7a-91ac-b0588be62dfd&amp;documentId=e122fe1a-f890-46e6-b6c5-bbffcf42c248</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2BM-7736128605-773601001-201603211141413966693</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <f>"7736128605"</f>
+        <v/>
+      </c>
+      <c r="B87">
+        <f>"773601001"</f>
+        <v/>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>АНО ДПО "КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА", КОРПОРАТИВНЫЙ УНИВЕРСИТЕТ СБЕРБАНКА, СБЕРУНИВЕРСИТЕТ</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7736128605 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E87">
+        <f>"LBO-LE-7736128605"</f>
+        <v/>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Ожидается промежуточная подпись</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>22.04.2026 15:09:00</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=8fcbde8c-a54b-4aa8-b1fc-8f347506da06&amp;documentId=5fe84401-17ba-4796-be79-25c84ee55233</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2BM-7736128605-773601001-201603211141413966693</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <f>"7730269550"</f>
+        <v/>
+      </c>
+      <c r="B88">
+        <f>"773001001"</f>
+        <v/>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ООО "СБЕР БИЗНЕС СОФТ"</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7730269550 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E88">
+        <f>"LBO-LE-7730269550"</f>
+        <v/>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Требуется подписать и отправить</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>21.04.2026 18:21:23</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=29bfe4ac-ee45-4a7c-a0a6-3706a6313fe1&amp;documentId=1ef45b11-331d-4c00-a460-f941e0241378</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <f>"7750005725"</f>
+        <v/>
+      </c>
+      <c r="B89">
+        <f>"770501001"</f>
+        <v/>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ООО НКО "ЮМАНИ"</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Доп. соглашение №LBO-LE-7750005725 от 21.04.26</t>
+        </is>
+      </c>
+      <c r="E89">
+        <f>"LBO-LE-7750005725"</f>
+        <v/>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>RUB - Российский рубль</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Требуется подписать и отправить</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>21.04.2026 19:16:56</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Головное подразделение -&gt; BizDev (А. Данилина) </t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Соглашение о передаче прав и обязанностей по договору облачного сервиса GigaChat в ООО «Салют для Бизнеса». Дополнительно (отдельным пакетом) отправлено информационное письмо посредством ЭДО. По вопросам соглашения обращаться: sales-soft@sberdevices.ru</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
           <t>https://diadoc.kontur.ru/4100c1d3-2464-4c71-95cc-21ba90d0c907/Document/Show?letterId=39806f2a-8c12-473e-a17c-dd06b299dcbd&amp;documentId=5b391afa-8066-4de5-9e26-a852b4a66510</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V67"/>
+  <autoFilter ref="A1:V89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>